--- a/Web-Tools/Cooking Corner/Rezepte.xlsx
+++ b/Web-Tools/Cooking Corner/Rezepte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mario/Documents/GitHub/homepage/Web-Tools/Cooking Corner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1B11C6-B885-5741-B097-7C8FA24AC167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A98988-89EC-1A4E-9EE8-2A847E3C9946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Numbers" sheetId="1" r:id="rId1"/>
@@ -134,21 +134,6 @@
     <t>Food</t>
   </si>
   <si>
-    <t>500g Mehl Typ 00
-650ml Wasser (Raumtemperatur)
-2g Trockenhefe
-1 Esslöffel Salz (gehäuft)
-2 Esslöffel Olivenöl</t>
-  </si>
-  <si>
-    <t>Hefe im Wasser auflösen und langsam im Mehl einkneten.
-Wenn der Teig geschmeidig ist Salz und Öl für ca. 15 Minuten einkneten.
-Anschließend abgedeckt 1 Stunde gehen lassen.
-Danach für 24 Stunden im Kühlschrank gehen lassen und 1 Mal falten.
-Weitere 24 Stunden im Kühlschrank gehen lassen und Teiglinge formen.
-Wieder gehen lassen und belegen. Mit der Hand vorsichtig die Pizzen formen - nicht ausrollen!</t>
-  </si>
-  <si>
     <t>Teig:
 200g Mehl
 3 EL Wasser
@@ -2153,6 +2138,20 @@
   </si>
   <si>
     <t>0034</t>
+  </si>
+  <si>
+    <t>1kg Mehl Typ 00
+620ml kaltes Wasser
+2g Trockenhefe
+30g Salz</t>
+  </si>
+  <si>
+    <t>2g Hefe in 100ml Wasser auflösen.
+30g Salz in 520ml Wasser auflösen.
+Pizzamehl mit dem Hefewasser vermischen.
+Salzwasser dazurühren und für etwa 15 min. kneten.
+Teig für 1-2 Stunden an einem warmen Ort gehen lassen. Danach in 6 Teile teilen und im Kühlschrank für 2-3 Tage gehen lassen.
+Teig einfrieren oder nochmal 1 Stunde an einem warmen Ort gehen lassen.</t>
   </si>
 </sst>
 </file>
@@ -2799,10 +2798,10 @@
         <v>19</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>21</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="289" x14ac:dyDescent="0.2">
@@ -2816,1319 +2815,1319 @@
         <v>19</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="E6" s="16" t="s">
         <v>29</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>71</v>
-      </c>
       <c r="E18" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="E19" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="E22" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="E24" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="238" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="238" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="238" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="E29" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="E30" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="E31" s="16" t="s">
         <v>129</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="E34" s="16" t="s">
         <v>141</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="16" t="s">
         <v>144</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="E36" s="16" t="s">
         <v>148</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>151</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="238" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="D50" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="E50" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="E51" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="E52" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="E53" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="E54" s="16" t="s">
         <v>221</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="340" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="E55" s="16" t="s">
         <v>225</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="E56" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D57" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="E59" s="16" t="s">
         <v>241</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="E60" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="255" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>248</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="306" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D62" s="12" t="s">
+      <c r="E62" s="16" t="s">
         <v>254</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B63" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="C63" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="16" t="s">
         <v>257</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="E65" s="16" t="s">
         <v>265</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B66" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="E66" s="16" t="s">
         <v>269</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="153" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="E67" s="16" t="s">
         <v>274</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A70" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="136" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>291</v>
-      </c>
       <c r="E71" s="16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D72" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="E72" s="16" t="s">
         <v>294</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="306" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="E73" s="16" t="s">
         <v>298</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E74" s="16" t="s">
         <v>301</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="E75" s="16" t="s">
         <v>305</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="E76" s="16" t="s">
         <v>309</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="187" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="E77" s="16" t="s">
         <v>313</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="E77" s="16" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B78" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="E78" s="16" t="s">
         <v>319</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E78" s="16" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D79" s="12" t="s">
+      <c r="E79" s="16" t="s">
         <v>324</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D80" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="E80" s="16" t="s">
         <v>328</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="5:5" x14ac:dyDescent="0.2">
@@ -5817,19 +5816,18 @@
         <v>Food</v>
       </c>
       <c r="D55" s="6" t="str">
-        <v>500g Mehl Typ 00
-650ml Wasser (Raumtemperatur)
+        <v>1kg Mehl Typ 00
+620ml kaltes Wasser
 2g Trockenhefe
-1 Esslöffel Salz (gehäuft)
-2 Esslöffel Olivenöl</v>
+30g Salz</v>
       </c>
       <c r="E55" s="6" t="str">
-        <v>Hefe im Wasser auflösen und langsam im Mehl einkneten.
-Wenn der Teig geschmeidig ist Salz und Öl für ca. 15 Minuten einkneten.
-Anschließend abgedeckt 1 Stunde gehen lassen.
-Danach für 24 Stunden im Kühlschrank gehen lassen und 1 Mal falten.
-Weitere 24 Stunden im Kühlschrank gehen lassen und Teiglinge formen.
-Wieder gehen lassen und belegen. Mit der Hand vorsichtig die Pizzen formen - nicht ausrollen!</v>
+        <v>2g Hefe in 100ml Wasser auflösen.
+30g Salz in 520ml Wasser auflösen.
+Pizzamehl mit dem Hefewasser vermischen.
+Salzwasser dazurühren und für etwa 15 min. kneten.
+Teig für 1-2 Stunden an einem warmen Ort gehen lassen. Danach in 6 Teile teilen und im Kühlschrank für 2-3 Tage gehen lassen.
+Teig einfrieren oder nochmal 1 Stunde an einem warmen Ort gehen lassen.</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
